--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議106件／要確認20件／未対応7件／要内訳1件／暫定6件 の計140箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議106件／要確認21件／未対応7件／要内訳1件／暫定6件 の計141箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議106件／要確認20件／未対応7件／要内訳1件／暫定6件 の計140箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議106件／要確認21件／未対応7件／要内訳1件／暫定6件 の計141箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の140箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る53箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の141箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る54箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（140箇所の所在）】</t>
+          <t>【章節別の未決箇所（141箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1631,18 +1631,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="F23" s="7" t="n">
         <v>0</v>
       </c>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>決定7</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
@@ -1667,17 +1667,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0</v>
@@ -1703,17 +1703,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>決定2</t>
+          <t>決定7</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
@@ -1734,25 +1734,25 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E26" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="F26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定2</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr"/>
@@ -1770,25 +1770,25 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>決定4</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
@@ -1806,22 +1806,22 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>決定6</t>
+          <t>決定4</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr"/>
@@ -1847,17 +1847,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>0</v>
@@ -1883,14 +1883,14 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
@@ -1919,17 +1919,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>4</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>0</v>
@@ -1955,17 +1955,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>0</v>
@@ -1986,22 +1986,22 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>0</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>決定1・決定2</t>
+          <t>決定6</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
@@ -2027,14 +2027,14 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>決定3</t>
+          <t>決定1・決定2</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr"/>
@@ -2063,14 +2063,14 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>0</v>
@@ -2079,14 +2079,14 @@
         <v>0</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>決定3・決定8</t>
+          <t>決定3</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr"/>
@@ -2099,30 +2099,30 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>決定3</t>
+          <t>決定3・決定8</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr"/>
@@ -2135,17 +2135,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="7" t="n">
         <v>0</v>
@@ -2154,11 +2154,11 @@
         <v>0</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>決定8</t>
+          <t>決定3</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr"/>
@@ -2166,35 +2166,35 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>資料編</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>資料6 基本指針の新別表「確認すべき指標・状況」への対応</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定8</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr"/>
@@ -2207,68 +2207,104 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
+          <t>資料6 基本指針の新別表「確認すべき指標・状況」への対応</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>決定10</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>資料編</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
           <t>資料7 図表番号一覧</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C40" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="7" t="n">
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>決定10</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr"/>
-      <c r="C40" s="15" t="n">
-        <v>140</v>
-      </c>
-      <c r="D40" s="15" t="n">
+      <c r="B41" s="14" t="inlineStr"/>
+      <c r="C41" s="15" t="n">
+        <v>141</v>
+      </c>
+      <c r="D41" s="15" t="n">
         <v>106</v>
       </c>
-      <c r="E40" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="F40" s="15" t="n">
+      <c r="E41" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="F41" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="G40" s="15" t="n">
+      <c r="G41" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="15" t="n">
+      <c r="H41" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="I40" s="15" t="inlineStr">
+      <c r="I41" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="J40" s="14" t="inlineStr"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="J41" s="14" t="inlineStr"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>注4）本表は協議用素案（令和8年8月時点）の本文及び表から機械的に抽出したものである。手作業で数えたものではない。注5）第6章第4節（施設の見込み）に15箇所が集中している。24時間対応サービスの整備の可否と介護医療院の区域外利用の扱いが未決であるためである。</t>
         </is>
@@ -2277,7 +2313,7 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A43:J43"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A17:J17"/>
   </mergeCells>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議106件／要確認21件／未対応7件／要内訳1件／暫定6件 の計141箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議110件／要確認27件／未対応7件／要内訳1件／暫定8件 の計153箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議106件／要確認21件／未対応7件／要内訳1件／暫定6件 の計141箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議110件／要確認27件／未対応7件／要内訳1件／暫定8件 の計153箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>区域内に事業所が存在しない4サービスについて、整備するか区域外利用を前提とするかを決定いただきたい。H12の代理指標20.4％は、この検討の参考情報の一つとする（在宅生活の維持が難しい利用者98票中20票の割合であり、在宅利用者全体の未充足率ではない）。整備の可否は、給付実績、町外利用、待機、事業者の参入意向・人員確保、利用意向及び費用影響を併せて判断する。</t>
+          <t>区域内に事業所が存在しない4サービスについて、整備するか区域外利用を前提とするかを決定いただきたい。H12の代理指標20.2％は、この検討の参考情報の一つとする（調査対象となった利用者99票中20票の割合であり、在宅利用者全体の未充足率ではない）。整備の可否は、給付実績、町外利用、待機、事業者の参入意向・人員確保、利用意向及び費用影響を併せて判断する。</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の141箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る54箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の153箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る66箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（141箇所の所在）】</t>
+          <t>【章節別の未決箇所（153箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1554,19 +1554,19 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0</v>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>決定1</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
@@ -1590,22 +1590,22 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>決定11</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr"/>
@@ -1626,12 +1626,12 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
@@ -1667,14 +1667,14 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>0</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>決定7</t>
+          <t>決定1</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>決定7</t>
+          <t>決定11</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
@@ -1739,17 +1739,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>決定2</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr"/>
@@ -1770,25 +1770,25 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定7</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
@@ -1806,22 +1806,22 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>決定4</t>
+          <t>決定7</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr"/>
@@ -1842,22 +1842,22 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>決定6</t>
+          <t>決定2</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr"/>
@@ -1878,25 +1878,25 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>決定6</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr"/>
@@ -1914,19 +1914,19 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>決定6</t>
+          <t>決定4</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>0</v>
@@ -2022,19 +2022,19 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>決定1・決定2</t>
+          <t>決定6</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr"/>
@@ -2058,22 +2058,22 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>0</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>決定3</t>
+          <t>決定6</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr"/>
@@ -2094,35 +2094,35 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>決定3・決定8</t>
+          <t>決定6</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr"/>
@@ -2135,17 +2135,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37" s="7" t="n">
         <v>0</v>
@@ -2154,11 +2154,11 @@
         <v>0</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>決定3</t>
+          <t>決定1・決定2</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr"/>
@@ -2171,17 +2171,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>0</v>
@@ -2190,11 +2190,11 @@
         <v>0</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>決定8</t>
+          <t>決定3</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr"/>
@@ -2202,35 +2202,35 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>資料編</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>資料6 基本指針の新別表「確認すべき指標・状況」への対応</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定3・決定8</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
@@ -2238,73 +2238,217 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>決定3</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>決定10</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>決定8</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
           <t>資料編</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>資料6 基本指針の新別表「確認すべき指標・状況」への対応</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>決定10</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>資料編</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>資料7 図表番号一覧</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C44" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="7" t="n">
+      <c r="D44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>決定10</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr"/>
-      <c r="C41" s="15" t="n">
-        <v>141</v>
-      </c>
-      <c r="D41" s="15" t="n">
-        <v>106</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>21</v>
-      </c>
-      <c r="F41" s="15" t="n">
+      <c r="B45" s="14" t="inlineStr"/>
+      <c r="C45" s="15" t="n">
+        <v>153</v>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="F45" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="G45" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
+      <c r="H45" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="J41" s="14" t="inlineStr"/>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="J45" s="14" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>注4）本表は協議用素案（令和8年8月時点）の本文及び表から機械的に抽出したものである。手作業で数えたものではない。注5）第6章第4節（施設の見込み）に15箇所が集中している。24時間対応サービスの整備の可否と介護医療院の区域外利用の扱いが未決であるためである。</t>
         </is>
@@ -2312,8 +2456,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A47:J47"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A43:J43"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A17:J17"/>
   </mergeCells>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議110件／要確認27件／未対応7件／要内訳1件／暫定8件 の計153箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議118件／要確認39件／未対応8件／要内訳1件／暫定8件 の計174箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議110件／要確認27件／未対応7件／要内訳1件／暫定8件 の計153箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議118件／要確認39件／未対応8件／要内訳1件／暫定8件 の計174箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の153箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る66箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の174箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る87箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（153箇所の所在）】</t>
+          <t>【章節別の未決箇所（174箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1595,14 +1595,14 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>1</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
@@ -1662,22 +1662,22 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>決定1</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr"/>
@@ -1698,25 +1698,25 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>決定11</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
@@ -1739,17 +1739,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定1</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr"/>
@@ -1775,17 +1775,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>決定7</t>
+          <t>決定11</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
@@ -1811,17 +1811,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>決定7</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr"/>
@@ -1847,17 +1847,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>決定2</t>
+          <t>決定7</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr"/>
@@ -1878,25 +1878,25 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定7</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr"/>
@@ -1914,22 +1914,22 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>決定4</t>
+          <t>決定2</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
@@ -1950,26 +1950,26 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" s="7" t="n">
         <v>0</v>
       </c>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>決定6</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr"/>
@@ -1986,12 +1986,12 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>決定6</t>
+          <t>決定4</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
@@ -2027,17 +2027,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>0</v>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>0</v>
@@ -2099,17 +2099,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>0</v>
@@ -2130,22 +2130,22 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="7" t="n">
         <v>0</v>
@@ -2154,11 +2154,11 @@
         <v>0</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>決定1・決定2</t>
+          <t>決定6</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr"/>
@@ -2166,22 +2166,22 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>決定3</t>
+          <t>決定6</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr"/>
@@ -2207,30 +2207,30 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>決定3・決定8</t>
+          <t>決定1・決定2</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
@@ -2243,17 +2243,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F40" s="7" t="n">
         <v>0</v>
@@ -2279,14 +2279,14 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>1</v>
@@ -2295,14 +2295,14 @@
         <v>0</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定3・決定8</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr"/>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F42" s="7" t="n">
         <v>0</v>
@@ -2334,11 +2334,11 @@
         <v>0</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>決定8</t>
+          <t>決定3</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr"/>
@@ -2346,25 +2346,25 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>資料編</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>資料6 基本指針の新別表「確認すべき指標・状況」への対応</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -2382,73 +2382,181 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>決定8</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>決定10</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>資料編</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>資料6 基本指針の新別表「確認すべき指標・状況」への対応</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>決定10</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>資料編</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>資料7 図表番号一覧</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C47" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="7" t="n">
+      <c r="D47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>決定10</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr"/>
-      <c r="C45" s="15" t="n">
-        <v>153</v>
-      </c>
-      <c r="D45" s="15" t="n">
-        <v>110</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="G45" s="15" t="n">
+      <c r="B48" s="14" t="inlineStr"/>
+      <c r="C48" s="15" t="n">
+        <v>174</v>
+      </c>
+      <c r="D48" s="15" t="n">
+        <v>118</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="F48" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="15" t="n">
+      <c r="H48" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="I45" s="15" t="inlineStr">
+      <c r="I48" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="J45" s="14" t="inlineStr"/>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="J48" s="14" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>注4）本表は協議用素案（令和8年8月時点）の本文及び表から機械的に抽出したものである。手作業で数えたものではない。注5）第6章第4節（施設の見込み）に15箇所が集中している。24時間対応サービスの整備の可否と介護医療院の区域外利用の扱いが未決であるためである。</t>
         </is>
@@ -2456,8 +2564,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A47:J47"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A50:J50"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A17:J17"/>
   </mergeCells>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議118件／要確認39件／未対応8件／要内訳1件／暫定8件 の計174箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議119件／要確認43件／未対応8件／要内訳1件／暫定8件 の計179箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議118件／要確認39件／未対応8件／要内訳1件／暫定8件 の計174箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議119件／要確認43件／未対応8件／要内訳1件／暫定8件 の計179箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の174箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る87箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の179箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る92箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（174箇所の所在）】</t>
+          <t>【章節別の未決箇所（179箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>0</v>
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>0</v>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>7</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>0</v>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>6</v>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>6</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>0</v>
@@ -2531,13 +2531,13 @@
       </c>
       <c r="B48" s="14" t="inlineStr"/>
       <c r="C48" s="15" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D48" s="15" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>8</v>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議119件／要確認43件／未対応8件／要内訳1件／暫定8件 の計179箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議121件／要確認57件／未対応8件／要内訳1件／暫定8件 の計195箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議119件／要確認43件／未対応8件／要内訳1件／暫定8件 の計179箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議121件／要確認57件／未対応8件／要内訳1件／暫定8件 の計195箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の179箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る92箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の195箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る108箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（179箇所の所在）】</t>
+          <t>【章節別の未決箇所（195箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>1</v>
@@ -2103,13 +2103,13 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>5</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>0</v>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" s="7" t="n">
         <v>0</v>
@@ -2247,13 +2247,13 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="7" t="n">
         <v>0</v>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>6</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>0</v>
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="7" t="n">
         <v>0</v>
@@ -2531,13 +2531,13 @@
       </c>
       <c r="B48" s="14" t="inlineStr"/>
       <c r="C48" s="15" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="D48" s="15" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>8</v>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議121件／要確認57件／未対応8件／要内訳1件／暫定8件 の計195箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議121件／要確認60件／未対応8件／要内訳1件／暫定8件 の計198箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議121件／要確認57件／未対応8件／要内訳1件／暫定8件 の計195箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議121件／要確認60件／未対応8件／要内訳1件／暫定8件 の計198箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の195箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る108箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の198箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る111箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（195箇所の所在）】</t>
+          <t>【章節別の未決箇所（198箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>0</v>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>7</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>0</v>
@@ -2531,13 +2531,13 @@
       </c>
       <c r="B48" s="14" t="inlineStr"/>
       <c r="C48" s="15" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D48" s="15" t="n">
         <v>121</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F48" s="15" t="n">
         <v>8</v>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議121件／要確認60件／未対応8件／要内訳1件／暫定8件 の計198箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議136件／要確認90件／未対応8件／要内訳2件／暫定9件 の計245箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議121件／要確認60件／未対応8件／要内訳1件／暫定8件 の計198箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議136件／要確認90件／未対応8件／要内訳2件／暫定9件 の計245箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の198箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る111箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の245箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る158箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（198箇所の所在）】</t>
+          <t>【章節別の未決箇所（245箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
+          <t>第6節　計画の進行管理・推進体制</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定5</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
@@ -1667,17 +1667,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0</v>
@@ -1703,20 +1703,20 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="7" t="n">
-        <v>11</v>
-      </c>
       <c r="F25" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
@@ -1734,26 +1734,26 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D26" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="E26" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F26" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="G26" s="7" t="n">
         <v>0</v>
       </c>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>決定1</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr"/>
@@ -1775,17 +1775,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>決定11</t>
+          <t>決定1</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
@@ -1811,17 +1811,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>0</v>
@@ -1847,17 +1847,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>決定7</t>
+          <t>決定11</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr"/>
@@ -1883,17 +1883,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" s="7" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>決定7</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr"/>
@@ -1919,17 +1919,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>決定2</t>
+          <t>決定7</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
@@ -1950,25 +1950,25 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定7</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr"/>
@@ -1986,22 +1986,22 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>0</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>決定4</t>
+          <t>決定2</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
@@ -2022,22 +2022,22 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>0</v>
@@ -2058,22 +2058,22 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>0</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>決定6</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr"/>
@@ -2094,26 +2094,26 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>5</v>
       </c>
       <c r="E36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="G36" s="7" t="n">
         <v>0</v>
       </c>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>決定6</t>
+          <t>決定10</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr"/>
@@ -2130,19 +2130,19 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>3</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>決定6</t>
+          <t>決定4</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr"/>
@@ -2171,17 +2171,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="7" t="n">
         <v>0</v>
@@ -2226,11 +2226,11 @@
         <v>0</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>決定1・決定2</t>
+          <t>決定6</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
@@ -2238,19 +2238,19 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>1</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>決定3</t>
+          <t>決定6</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr"/>
@@ -2274,35 +2274,35 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="C41" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D41" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="E41" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>決定3・決定8</t>
+          <t>決定6</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr"/>
@@ -2310,22 +2310,22 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F42" s="7" t="n">
         <v>0</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>決定3</t>
+          <t>決定6</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr"/>
@@ -2351,30 +2351,30 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="C43" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定1・決定2</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr"/>
@@ -2387,17 +2387,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>0</v>
@@ -2406,11 +2406,11 @@
         <v>0</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>決定8</t>
+          <t>決定3</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr"/>
@@ -2423,30 +2423,30 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定3・決定8</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr"/>
@@ -2454,25 +2454,25 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>資料編</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>資料6 基本指針の新別表「確認すべき指標・状況」への対応</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E46" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="F46" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>0</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>決定10</t>
+          <t>決定3</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr"/>
@@ -2490,73 +2490,217 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>決定10</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>決定8</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>決定10</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
           <t>資料編</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>資料6 基本指針の新別表「確認すべき指標・状況」への対応</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>決定10</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>資料編</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>資料7 図表番号一覧</t>
         </is>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C51" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="7" t="n">
+      <c r="E51" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="F51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>決定10</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr"/>
-      <c r="C48" s="15" t="n">
-        <v>198</v>
-      </c>
-      <c r="D48" s="15" t="n">
-        <v>121</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="F48" s="15" t="n">
+      <c r="B52" s="14" t="inlineStr"/>
+      <c r="C52" s="15" t="n">
+        <v>245</v>
+      </c>
+      <c r="D52" s="15" t="n">
+        <v>136</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="F52" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="G48" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="I48" s="15" t="inlineStr">
+      <c r="G52" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="J48" s="14" t="inlineStr"/>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="J52" s="14" t="inlineStr"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>注4）本表は協議用素案（令和8年8月時点）の本文及び表から機械的に抽出したものである。手作業で数えたものではない。注5）第6章第4節（施設の見込み）に15箇所が集中している。24時間対応サービスの整備の可否と介護医療院の区域外利用の扱いが未決であるためである。</t>
         </is>
@@ -2565,7 +2709,7 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A54:J54"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A17:J17"/>
   </mergeCells>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議136件／要確認90件／未対応8件／要内訳2件／暫定9件 の計245箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議136件／要確認95件／未対応8件／要内訳2件／暫定9件 の計250箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議136件／要確認90件／未対応8件／要内訳2件／暫定9件 の計245箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議136件／要確認95件／未対応8件／要内訳2件／暫定9件 の計250箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の245箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る158箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の250箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る163箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（245箇所の所在）】</t>
+          <t>【章節別の未決箇所（250箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>1</v>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>0</v>
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>7</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>0</v>
@@ -2675,13 +2675,13 @@
       </c>
       <c r="B52" s="14" t="inlineStr"/>
       <c r="C52" s="15" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D52" s="15" t="n">
         <v>136</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F52" s="15" t="n">
         <v>8</v>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議136件／要確認95件／未対応8件／要内訳2件／暫定9件 の計250箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議138件／要確認102件／未対応8件／要内訳2件／暫定9件 の計259箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議136件／要確認95件／未対応8件／要内訳2件／暫定9件 の計250箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議138件／要確認102件／未対応8件／要内訳2件／暫定9件 の計259箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の250箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る163箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の259箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る172箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（250箇所の所在）】</t>
+          <t>【章節別の未決箇所（259箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>1</v>
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>0</v>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>0</v>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>6</v>
@@ -2675,13 +2675,13 @@
       </c>
       <c r="B52" s="14" t="inlineStr"/>
       <c r="C52" s="15" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="D52" s="15" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F52" s="15" t="n">
         <v>8</v>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議138件／要確認102件／未対応8件／要内訳2件／暫定9件 の計259箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議142件／要確認109件／未対応8件／要内訳2件／暫定9件 の計270箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議138件／要確認102件／未対応8件／要内訳2件／暫定9件 の計259箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議142件／要確認109件／未対応8件／要内訳2件／暫定9件 の計270箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の259箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る172箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の270箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る183箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（259箇所の所在）】</t>
+          <t>【章節別の未決箇所（270箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>1</v>
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>0</v>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>7</v>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>0</v>
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>7</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" s="7" t="n">
         <v>0</v>
@@ -2675,13 +2675,13 @@
       </c>
       <c r="B52" s="14" t="inlineStr"/>
       <c r="C52" s="15" t="n">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D52" s="15" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F52" s="15" t="n">
         <v>8</v>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議142件／要確認109件／未対応8件／要内訳2件／暫定9件 の計270箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議158件／要確認113件／未対応8件／要内訳2件／暫定9件 の計290箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議142件／要確認109件／未対応8件／要内訳2件／暫定9件 の計270箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議158件／要確認113件／未対応8件／要内訳2件／暫定9件 の計290箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の270箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る183箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の290箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る203箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（270箇所の所在）】</t>
+          <t>【章節別の未決箇所（290箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>1</v>
@@ -1599,13 +1599,13 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0</v>
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>1</v>
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>0</v>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>0</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>1</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>3</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>11</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F42" s="7" t="n">
         <v>0</v>
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>0</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" s="7" t="n">
         <v>6</v>
-      </c>
-      <c r="D45" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>1</v>
@@ -2675,13 +2675,13 @@
       </c>
       <c r="B52" s="14" t="inlineStr"/>
       <c r="C52" s="15" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="D52" s="15" t="n">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F52" s="15" t="n">
         <v>8</v>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>0</v>
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>13</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>1</v>

--- a/output/第10期計画_発注者確認事項一覧.xlsx
+++ b/output/第10期計画_発注者確認事項一覧.xlsx
@@ -594,7 +594,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議158件／要確認113件／未対応8件／要内訳2件／暫定9件 の計290箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
+          <t>計画素案に残る要協議158件／要確認115件／未対応8件／要内訳2件／暫定9件 の計292箇所を、ご決定いただく単位で12件に集約したものです。策定委員会では本一覧を審議事項の要約としてご使用いただき、計画本文の該当箇所を併せてご参照ください。</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案に残る要協議158件／要確認113件／未対応8件／要内訳2件／暫定9件 の計290箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
+          <t>計画素案に残る要協議158件／要確認115件／未対応8件／要内訳2件／暫定9件 の計292箇所を、決定の単位で12件にまとめた。策定委員会では本一覧を審議事項の要約として用い、計画本文の該当箇所を併せて参照する。</t>
         </is>
       </c>
     </row>
@@ -1492,14 +1492,14 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>注1）箇所数の合計は87箇所である。本文の290箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る203箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
+          <t>注1）箇所数の合計は87箇所である。本文の292箇所のうち、決定12（概要版の仕様）は本文にプレースホルダを持たないため0としている。残る205箇所は複数の決定にまたがるか、資料の受領により自動的に解消するものである。注2）本文のプレースホルダは残す方針を維持する。本文に確認事項の注記を書かず、別管理表で一元管理する運用によるものである。注3）委員会資料では、本一覧の推奨案を示したうえで確定値と暫定値を視覚的に分ける。本一覧は審議事項の要約であり、計画本文の該当箇所を併せて参照していただく。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【章節別の未決箇所（290箇所の所在）】</t>
+          <t>【章節別の未決箇所（292箇所の所在）】</t>
         </is>
       </c>
     </row>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>0</v>
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>6</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="7" t="n">
         <v>0</v>
@@ -2675,13 +2675,13 @@
       </c>
       <c r="B52" s="14" t="inlineStr"/>
       <c r="C52" s="15" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D52" s="15" t="n">
         <v>158</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F52" s="15" t="n">
         <v>8</v>
